--- a/Logical Model Template.xlsx
+++ b/Logical Model Template.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -585,12 +585,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Data Set X, columns M-N</t>
+          <t>Data Set X, column M</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Map the element to a Common Glossary concept: the concept code, and how it relates to this element. Leave blank if there is no matching concept.</t>
+          <t>How firmly the ValueSet binds: required (only these codes), extensible (these unless none fits), preferred (these are recommended) or example. Blank means preferred.</t>
         </is>
       </c>
     </row>
@@ -602,10 +602,27 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>Data Set X, columns N-O</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Map the element to a Common Glossary concept: the concept code, and how it relates to this element. Leave blank if there is no matching concept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Terminologist</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>VS&lt;Name&gt;</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>The codes allowed for a coded element, with the code system they come from.</t>
         </is>
@@ -758,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -773,10 +790,11 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -790,17 +808,17 @@
           <t>Data Element</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Common Glossary</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Example Value</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Example Value Display Name (for coded values)</t>
         </is>
@@ -865,16 +883,21 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
+          <t>Binding Strength</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>Relationship</t>
         </is>
       </c>
-      <c r="O2" s="3" t="n"/>
       <c r="P2" s="3" t="n"/>
+      <c r="Q2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -912,19 +935,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>RecordedDate</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>equivalent</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
         </is>
       </c>
     </row>
@@ -969,12 +987,17 @@
           <t>VSAllergyType</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>required</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
+        <is>
+          <t>Allergy</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Allergy</t>
         </is>
@@ -982,8 +1005,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="B1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -995,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1010,10 +1033,11 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1027,17 +1051,17 @@
           <t>Data Element</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Common Glossary</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Example Value</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Example Value Display Name (for coded values)</t>
         </is>
@@ -1102,21 +1126,26 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
+          <t>Binding Strength</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>Relationship</t>
         </is>
       </c>
-      <c r="O2" s="3" t="n"/>
       <c r="P2" s="3" t="n"/>
+      <c r="Q2" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="B1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
